--- a/reports/jobs_2026-10-13.xlsx
+++ b/reports/jobs_2026-10-13.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -538,7 +538,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -546,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/seattle-wa/R-110306-2/</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -563,17 +567,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -589,12 +593,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/austin-tx/R-110306/</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -606,17 +610,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -624,7 +628,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -632,12 +640,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/seattle-wa/R-110379-2/</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -649,17 +657,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -667,7 +675,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -675,12 +687,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/san-jose-ca/R-110379-1/</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -692,17 +704,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -710,7 +722,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -718,12 +734,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/austin-tx/R-110379/</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -735,17 +751,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Principle Engineer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -753,7 +769,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -761,12 +781,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/san-jose-ca/R-110306-1/</t>
+          <t>https://www.atlassian.com/company/careers/details/27074</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -778,17 +798,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -796,7 +816,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -804,12 +828,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -821,17 +845,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -847,12 +871,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -864,17 +888,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -890,12 +914,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/san-jose-ca/R-110382-1/</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -907,681 +931,689 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>AI / ML</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, 2027 Graduate Canada</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>AI / ML</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Research Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, 2027 Canada</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Product Security Engineer</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Chiang Mai 0 available jobs</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/27475</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Security Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Dubai 0 available jobs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian India</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Security Engineer</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Shanghai 1 available jobs</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Engineering &amp; Technology</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/department/technology/</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Backend Developer Jobs</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Full Stack Developer Jobs</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Agoda India</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer Jobs</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>https://careersatagoda.com/</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Atlassian India</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Security Testing Engineer - Penetration Tester</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>QA / SDET</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Atlassian India</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>AI and Machine Learning</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>AI / ML</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1602,12 +1634,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1619,12 +1651,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Chiang Mai 0 available jobs</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1637,7 +1669,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 1 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -1645,12 +1681,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1662,17 +1698,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1682,7 +1718,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Electronic City,  Bengaluru, in</t>
+          <t>Mumbai 1 available jobs Ok</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1692,12 +1728,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1709,12 +1745,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Mumbai 1 available jobs</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1729,7 +1765,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Mumbai 1 available jobs Ok</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1739,12 +1775,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1756,17 +1792,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1776,7 +1812,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Mumbai 1 available jobs Ok</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1786,12 +1822,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1803,12 +1839,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1821,11 +1857,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -1833,12 +1865,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1850,12 +1882,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1868,11 +1900,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -1880,12 +1908,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1897,17 +1925,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1923,12 +1951,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1940,12 +1968,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1960,7 +1988,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Mumbai jobs Yokohama jobs</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1970,12 +1998,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -1987,17 +2015,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2005,11 +2033,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2017,12 +2041,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2034,17 +2058,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2052,11 +2076,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2064,12 +2084,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2081,12 +2101,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2099,11 +2119,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2111,12 +2127,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2128,17 +2144,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2148,7 +2164,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2158,12 +2174,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2175,12 +2191,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2193,11 +2209,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2205,12 +2217,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2222,17 +2234,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2240,11 +2252,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2252,12 +2260,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2269,17 +2277,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2287,7 +2295,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Electronic City,  Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2295,12 +2307,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2312,12 +2324,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2330,7 +2342,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2338,12 +2354,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2355,17 +2371,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AI Governance Arcitect</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2373,7 +2389,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2381,12 +2401,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2398,17 +2418,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2416,7 +2436,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2424,12 +2448,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2441,12 +2465,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2459,7 +2483,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2467,12 +2495,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2484,17 +2512,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2510,12 +2538,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2527,12 +2555,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2545,7 +2573,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2553,12 +2585,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2570,17 +2602,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2590,7 +2622,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2600,12 +2632,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2617,17 +2649,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2637,7 +2669,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2647,12 +2679,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2664,12 +2696,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2684,7 +2716,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2694,12 +2726,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2711,17 +2743,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2731,7 +2763,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2741,12 +2773,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2758,17 +2790,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2778,7 +2810,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2788,12 +2820,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2805,17 +2837,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2823,7 +2855,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2831,12 +2867,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2848,17 +2884,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2874,12 +2910,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/san-jose-ca/R-110379-1/</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2891,17 +2927,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2909,11 +2945,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2921,12 +2953,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/seattle-wa/R-110306-2/</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2938,17 +2970,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2956,11 +2988,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2968,12 +2996,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/san-jose-ca/R-110306-1/</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -2985,17 +3013,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3011,12 +3039,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/austin-tx/R-110306/</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3028,17 +3056,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3046,11 +3074,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3058,12 +3082,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/seattle-wa/R-110379-2/</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3075,17 +3099,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3101,12 +3125,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/austin-tx/R-110379/</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3118,17 +3142,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3136,11 +3160,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, India</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3148,12 +3168,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3165,17 +3185,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3183,11 +3203,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>India’s 100 th unicorn. C</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3195,12 +3211,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers.html</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/san-jose-ca/R-110382-1/</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3212,12 +3228,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3238,12 +3254,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3255,17 +3271,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3273,11 +3289,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3285,12 +3297,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3302,12 +3314,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3320,11 +3332,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3332,12 +3340,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3349,17 +3357,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3367,11 +3375,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3379,12 +3383,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3396,12 +3400,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3416,7 +3420,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3426,12 +3430,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3443,12 +3447,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3463,7 +3467,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3473,12 +3477,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3490,12 +3494,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3508,7 +3512,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3516,12 +3524,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3533,17 +3541,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3553,7 +3561,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3563,12 +3571,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3580,17 +3588,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3600,7 +3608,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3610,12 +3618,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3627,17 +3635,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3645,11 +3653,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3657,12 +3661,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3674,17 +3678,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3700,12 +3704,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3717,12 +3721,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3737,7 +3741,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3747,12 +3751,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3764,17 +3768,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3784,7 +3788,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3794,12 +3798,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3811,12 +3815,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3829,11 +3833,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3905,17 +3905,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3923,11 +3923,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3935,12 +3931,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3952,17 +3948,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3972,7 +3968,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3982,12 +3978,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -3999,12 +3995,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4014,12 +4010,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>India’s 100 th unicorn. C</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4029,12 +4025,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://open.money/company/careers.html</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4046,12 +4042,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4064,11 +4060,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4076,12 +4068,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4093,17 +4085,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4113,7 +4105,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4123,12 +4115,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4140,12 +4132,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4158,7 +4150,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4166,12 +4162,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4183,17 +4179,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4201,7 +4197,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4226,17 +4226,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4244,7 +4244,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4252,12 +4256,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4269,17 +4273,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4287,7 +4291,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4295,12 +4303,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4312,12 +4320,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4338,12 +4346,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4355,17 +4363,17 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4375,7 +4383,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4385,12 +4393,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4402,17 +4410,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4422,7 +4430,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4432,12 +4440,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4449,17 +4457,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4467,7 +4475,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -4475,12 +4487,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -4492,12 +4504,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4518,12 +4530,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4535,17 +4547,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4565,12 +4577,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4582,12 +4594,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4602,7 +4614,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon, India; Pune, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -4612,12 +4624,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4629,12 +4641,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4649,7 +4661,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -4659,12 +4671,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4676,52 +4688,917 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - Cloud: Azure</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (CPD) - Winter Intern</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - IAM</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer- SaaS O365</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - Winter Intern</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Scaler</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>AI Screenplay Writer</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>AI Video Editor</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>AI Sound Designer</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>AI Animator</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>QA / SDET</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>SirionLabs</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Intern- Employee Engagement</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sirionlabs.com/careers/</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Sprinklr</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Internship and Early Careers</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Software Procurement Intern</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Gurgaon, India; Pune, India</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I94"/>
+  <autoFilter ref="A1:I113"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4816,6 +5693,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4827,7 +5723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4875,15 +5771,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.indmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4892,26 +5808,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rocketlane</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.rocketlane.com/careers</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.rocketlane.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4935,15 +5831,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Ather Energy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.atherenergy.com/careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4952,26 +5868,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ather Energy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.atherenergy.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -5035,35 +5931,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Darwinbox</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://darwinbox.com/careers</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5072,18 +5948,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5092,18 +5968,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5112,6 +5988,26 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -5155,15 +6051,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5172,18 +6088,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5192,18 +6108,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5212,18 +6128,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
